--- a/templates/pvwood_master_data.xlsx
+++ b/templates/pvwood_master_data.xlsx
@@ -14,11 +14,10 @@
     <sheet name="Supplier" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Customer" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Item" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Product" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="GlueRecipe" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="GlueRecipe_Components" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LogArrival" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Log" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="GlueRecipe" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="GlueRecipe_Components" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="LogArrival" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Log" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -485,19 +484,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>then Item / Product / GlueRecipe, then GlueRecipe_Components, LogArrival, Log.</t>
+          <t>then Item / GlueRecipe, then GlueRecipe_Components, LogArrival, Log.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Item.kind and Location.kind use dropdowns. Dimensions in mm. Costs per unit.</t>
+          <t>Products (finished SKUs) are defined in the BOM workbook's Assembly_BOM sheet, not here.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>Item.kind and Location.kind use dropdowns. Dimensions in mm. Costs per unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Logs: enter any one unit of length/diameter/volume — the system converts the rest.</t>
         </is>
@@ -509,70 +515,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ recipe_code</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>★ component_role</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>★ item_code</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>GL-STD</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>resin</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>GLU-UF-RESIN</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -643,7 +585,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1391,121 +1333,6 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ code</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>★ name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>category_code</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>thickness_mm</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>width_mm</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>length_mm</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>pallet_qty</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>revision</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>DS-OAK-3.2</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Oak Door Skin 3.2mm</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>DOORSKIN</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>915</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
@@ -1610,4 +1437,68 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>★ recipe_code</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>★ component_role</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>★ item_code</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>GL-STD</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>resin</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>GLU-UF-RESIN</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/templates/pvwood_master_data.xlsx
+++ b/templates/pvwood_master_data.xlsx
@@ -8,16 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Species" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ProductCategory" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="WarehouseLocation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Supplier" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Customer" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Item" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="GlueRecipe" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="GlueRecipe_Components" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="LogArrival" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Log" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="WarehouseLocation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Supplier" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Customer" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Item" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GlueRecipe" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="GlueRecipe_Components" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LogArrival" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Log" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -477,14 +475,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fill reference sheets first (Species, ProductCategory, WarehouseLocation, Supplier),</t>
+          <t>Fill reference sheets first (WarehouseLocation, Supplier), then Item / GlueRecipe,</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>then Item / GlueRecipe, then GlueRecipe_Components, LogArrival, Log.</t>
+          <t>then GlueRecipe_Components, LogArrival, Log.</t>
         </is>
       </c>
     </row>
@@ -498,233 +496,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Item.kind and Location.kind use dropdowns. Dimensions in mm. Costs per unit.</t>
+          <t>Type species freely on Item/Log (e.g. OAK); the system auto-masters the species list.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Item.kind and Location.kind use dropdowns. Dimensions in mm. Costs per unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Logs: enter any one unit of length/diameter/volume — the system converts the rest.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ arrival_code</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>arrival_date</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>supplier_code</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>container_ref</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ARR-2026-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>SUP001</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>MSKU1234567</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ log_number</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>★ arrival_code</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>★ log_code</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>species_code</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>grade</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>length_in</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>length_m</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>diameter_in</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>diameter_m</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>volume_ft3</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>volume_m3</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>LOG-0001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ARR-2026-001</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>OAK-A</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>photo in notes</t>
         </is>
       </c>
     </row>
@@ -734,119 +520,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ code</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>★ common_name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>botanical_name</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>White Oak</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Quercus alba</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ code</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>★ name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>DOORSKIN</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Door Skin</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Primed/UV door skins</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -911,7 +584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -996,7 +669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1066,7 +739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1081,7 +754,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -1133,7 +806,7 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>species_code</t>
+          <t>species</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
@@ -1324,7 +997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1439,7 +1112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1501,4 +1174,223 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>★ arrival_code</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>arrival_date</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>supplier_code</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>container_ref</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ARR-2026-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>SUP001</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>MSKU1234567</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>★ log_number</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>★ arrival_code</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>★ log_code</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>length_in</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>length_m</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>diameter_in</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>diameter_m</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>volume_ft3</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>volume_m3</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>LOG-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>ARR-2026-001</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>OAK-A</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>photo in notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/templates/pvwood_master_data.xlsx
+++ b/templates/pvwood_master_data.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,10 +35,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
     </font>
     <font>
       <b val="1"/>
@@ -70,16 +66,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -556,27 +551,9 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>WH-A1</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Warehouse A Rack 1</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>WAREHOUSE</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C3:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"WAREHOUSE,FC,WIP,FG,STAGING"</formula1>
     </dataValidation>
   </dataValidations>
@@ -590,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -639,31 +616,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SUP001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ACME Veneer Co</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>K. Somchai</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>0812345678</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -675,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -718,22 +670,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Global Doors Ltd</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>J. Smith</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -745,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -890,106 +826,9 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>VNR-OAK-CQ-A</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>VENEER</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Oak Crown A</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>CROWN</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>BOOK</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>FACE</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>FSC100</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="Q2" s="4" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="R2" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="S2" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>5201</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>SUP001</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B3:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"VENEER,BOARD,GLUE_COMPONENT,CONSUMABLE,PACKING,OTHER"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1003,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1064,49 +903,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>GL-STD</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Standard UF</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1118,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1149,28 +945,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>GL-STD</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>resin</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>GLU-UF-RESIN</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1182,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1219,29 +993,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ARR-2026-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>SUP001</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>MSKU1234567</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1253,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1332,64 +1083,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>LOG-0001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ARR-2026-001</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>OAK-A</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>photo in notes</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/pvwood_master_data.xlsx
+++ b/templates/pvwood_master_data.xlsx
@@ -12,10 +12,6 @@
     <sheet name="Supplier" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Customer" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Item" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GlueRecipe" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="GlueRecipe_Components" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="LogArrival" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Log" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -456,42 +452,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>★ = required column (shaded). Row 2 (grey italic) is an example — overwrite or delete it.</t>
+          <t>★ = required column (shaded). Data starts on row 2.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codes are your own identifiers; other sheets/BOMs reference rows by these codes.</t>
+          <t>Codes are your own identifiers; the BOM workbook references items by these codes.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fill reference sheets first (WarehouseLocation, Supplier), then Item / GlueRecipe,</t>
+          <t>Fill WarehouseLocation + Supplier first, then Item (all RM/consumables: boards,</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>then GlueRecipe_Components, LogArrival, Log.</t>
+          <t>veneers, glue components, packing, and LOGS — kind=LOG, e.g. LRO4S).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Products (finished SKUs) are defined in the BOM workbook's Assembly_BOM sheet, not here.</t>
+          <t>Products (finished SKUs) + glue recipes live in the BOM workbook, not here.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Type species freely on Item/Log (e.g. OAK); the system auto-masters the species list.</t>
+          <t>Type species freely on Item (e.g. OAK); the system auto-masters the species list.</t>
         </is>
       </c>
     </row>
@@ -499,13 +495,6 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>Item.kind and Location.kind use dropdowns. Dimensions in mm. Costs per unit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Logs: enter any one unit of length/diameter/volume — the system converts the rest.</t>
         </is>
       </c>
     </row>
@@ -829,261 +818,9 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"VENEER,BOARD,GLUE_COMPONENT,CONSUMABLE,PACKING,OTHER"</formula1>
+      <formula1>"VENEER,BOARD,LOG,GLUE_COMPONENT,CONSUMABLE,PACKING,OTHER"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ recipe_code</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>★ name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>resin_ratio</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>hardener_ratio</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>extender_ratio</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>filler_ratio</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>water_ratio</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>mix_time_min</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ recipe_code</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>★ component_role</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>★ item_code</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ arrival_code</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>arrival_date</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>supplier_code</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>container_ref</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>★ log_number</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>★ arrival_code</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>★ log_code</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>species</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>grade</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>length_in</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>length_m</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>diameter_in</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>diameter_m</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>volume_ft3</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>volume_m3</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>